--- a/ExportExcel/Login Tests.xlsx
+++ b/ExportExcel/Login Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -38,87 +38,40 @@
     <t/>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>4406 ms</t>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>0 ms</t>
   </si>
   <si>
     <t>testNonExistentEmail</t>
   </si>
   <si>
-    <t>2367 ms</t>
-  </si>
-  <si>
     <t>testInvalidEmailFormat</t>
   </si>
   <si>
-    <t>2397 ms</t>
-  </si>
-  <si>
     <t>testEmptyPassword</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>2269 ms</t>
-  </si>
-  <si>
-    <t>Cannot invoke "utils.PopupHandler.isPopupPresent(String)" because "this.popupHandler" is null</t>
-  </si>
-  <si>
     <t>testEmptyEmail</t>
   </si>
   <si>
-    <t>2212 ms</t>
-  </si>
-  <si>
     <t>testEmptyEmailAndPassword</t>
   </si>
   <si>
-    <t>7268 ms</t>
-  </si>
-  <si>
     <t>testInvalidEmailSpecialChars</t>
   </si>
   <si>
-    <t>2482 ms</t>
-  </si>
-  <si>
     <t>testShortPassword</t>
   </si>
   <si>
-    <t>2446 ms</t>
-  </si>
-  <si>
     <t>testEmailContainingSpaces</t>
   </si>
   <si>
-    <t>2508 ms</t>
-  </si>
-  <si>
     <t>testPasswordContainingSpaces</t>
   </si>
   <si>
-    <t>2418 ms</t>
-  </si>
-  <si>
-    <t>testPasswordVisibilityToggle</t>
-  </si>
-  <si>
-    <t>1462 ms</t>
-  </si>
-  <si>
-    <t>no such element: Unable to locate element: {"method":"css selector","selector":".fa-sharp.fa-solid.fa-eye-slash"}
-  (Session info: chrome=134.0.6998.178)
-For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Build info: version: '4.28.1', revision: '73f5ad48a2'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [ea081ad99841f4cb0ad1345c47edb280, findElement {using=css selector, value=.fa-sharp.fa-solid.fa-eye-slash}]
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:64673}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:64673/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: ea081ad99841f4cb0ad1345c47edb280</t>
+    <t>testPasswordVisibilityAsText</t>
   </si>
 </sst>
 </file>
@@ -191,9 +144,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="25.80859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -226,7 +179,7 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="1">
+      <c r="D2" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
@@ -246,11 +199,11 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="1">
+      <c r="D3" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -261,16 +214,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>7</v>
@@ -281,19 +234,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>15</v>
+      <c r="D5" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -301,19 +254,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>15</v>
+      <c r="D6" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -321,16 +274,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -341,16 +294,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>7</v>
@@ -361,16 +314,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -381,16 +334,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -401,16 +354,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="1">
+      <c r="D11" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>
@@ -421,19 +374,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>15</v>
+      <c r="D12" t="s" s="0">
+        <v>8</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/ExportExcel/Login Tests.xlsx
+++ b/ExportExcel/Login Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>STT</t>
   </si>
@@ -38,40 +38,70 @@
     <t/>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>5817 ms</t>
   </si>
   <si>
     <t>testNonExistentEmail</t>
   </si>
   <si>
+    <t>1718 ms</t>
+  </si>
+  <si>
     <t>testInvalidEmailFormat</t>
   </si>
   <si>
+    <t>2214 ms</t>
+  </si>
+  <si>
     <t>testEmptyPassword</t>
   </si>
   <si>
+    <t>2403 ms</t>
+  </si>
+  <si>
     <t>testEmptyEmail</t>
   </si>
   <si>
+    <t>2524 ms</t>
+  </si>
+  <si>
     <t>testEmptyEmailAndPassword</t>
   </si>
   <si>
+    <t>6645 ms</t>
+  </si>
+  <si>
     <t>testInvalidEmailSpecialChars</t>
   </si>
   <si>
+    <t>1769 ms</t>
+  </si>
+  <si>
     <t>testShortPassword</t>
   </si>
   <si>
+    <t>2082 ms</t>
+  </si>
+  <si>
     <t>testEmailContainingSpaces</t>
   </si>
   <si>
+    <t>1995 ms</t>
+  </si>
+  <si>
     <t>testPasswordContainingSpaces</t>
   </si>
   <si>
+    <t>2083 ms</t>
+  </si>
+  <si>
     <t>testPasswordVisibilityAsText</t>
+  </si>
+  <si>
+    <t>3049 ms</t>
   </si>
 </sst>
 </file>
@@ -144,7 +174,7 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="25.80859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
@@ -179,7 +209,7 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
@@ -199,11 +229,11 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -214,16 +244,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>7</v>
@@ -234,16 +264,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>7</v>
@@ -254,16 +284,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -274,16 +304,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -294,16 +324,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="D8" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>7</v>
@@ -314,16 +344,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="D9" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -334,16 +364,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="D10" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -354,16 +384,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="0">
+      <c r="D11" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>
@@ -374,16 +404,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="D12" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s" s="0">
         <v>7</v>
